--- a/nepal_building_damage_dictionary.xlsx
+++ b/nepal_building_damage_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\earthquake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A4EAD0-649B-4C23-B4A1-4C14FBD17CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BEFB5B-3FDE-4230-9C70-5D7E845B4597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="컬럼정의서" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="266">
   <si>
     <t>네팔 지진 건물 손상 컬럼정의서</t>
   </si>
@@ -1045,10 +1045,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1175,6 +1171,14 @@
       </rPr>
       <t>코드</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>has_superstructure_mud_mortar_stone</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">   has_superstructure_adobe_mud</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1718,10 +1722,10 @@
     </row>
     <row r="10" spans="1:10" ht="78" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
@@ -1750,7 +1754,7 @@
     </row>
     <row r="11" spans="1:10" ht="78" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>29</v>
@@ -2166,7 +2170,7 @@
     </row>
     <row r="24" spans="1:10" ht="78" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>96</v>
@@ -2198,10 +2202,10 @@
     </row>
     <row r="25" spans="1:10" ht="78" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>23</v>
